--- a/registration_forms/026_social_workers_membership_form--registration_forms.xlsx
+++ b/registration_forms/026_social_workers_membership_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'a',_'name':_'member'}</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'A', 'name': 'Member'}</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'b',_'name':_'associate'}</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'B', 'name': 'Associate'}</t>
+          <t>Associate</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'c',_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'C', 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'d',_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'D', 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'e',_'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'E', 'name': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'name':_'member'}</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '1', 'name': 'Member'}</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'name':_'non-member'}</t>
+          <t>non-member</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '2', 'name': 'Non-Member'}</t>
+          <t>Non-Member</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'name':_'category'}</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '1', 'name': 'Category'}</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'name':_'another_category'}</t>
+          <t>another_category</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '2', 'name': 'Another Category'}</t>
+          <t>Another Category</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'name':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '1', 'name': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'name':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '2', 'name': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'name':_'chicago'}</t>
+          <t>chicago</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '3', 'name': 'Chicago'}</t>
+          <t>Chicago</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'name':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '1', 'name': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'name':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '2', 'name': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'name':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': '3', 'name': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'4',_'name':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': '4', 'name': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'5',_'name':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': '5', 'name': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'6',_'name':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': '6', 'name': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'7',_'name':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': '7', 'name': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_'8',_'name':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': '8', 'name': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_'9',_'name':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': '9', 'name': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_'10',_'name':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': '10', 'name': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_'11',_'name':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': '11', 'name': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_'12',_'name':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': '12', 'name': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'name':_2010}</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': '1', 'name': 2010}</t>
+          <t>2010</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'name':_2011}</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': '2', 'name': 2011}</t>
+          <t>2011</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'name':_2012}</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': '3', 'name': 2012}</t>
+          <t>2012</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_'4',_'name':_2013}</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': '4', 'name': 2013}</t>
+          <t>2013</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_'5',_'name':_2014}</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': '5', 'name': 2014}</t>
+          <t>2014</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_'6',_'name':_2015}</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': '6', 'name': 2015}</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_'7',_'name':_2016}</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': '7', 'name': 2016}</t>
+          <t>2016</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_'8',_'name':_2017}</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': '8', 'name': 2017}</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_'9',_'name':_2018}</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': '9', 'name': 2018}</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_'10',_'name':_2019}</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': '10', 'name': 2019}</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_'11',_'name':_2020}</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': '11', 'name': 2020}</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_'12',_'name':_2021}</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': '12', 'name': 2021}</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_'13',_'name':_2022}</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': '13', 'name': 2022}</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
